--- a/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_RackDrivenShafts.xlsx
+++ b/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack_RackDrivenShafts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\Rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43C7A0C-63FB-4142-BD30-696BFC464FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5B6DF2-0849-47B8-8AA2-7C1A96F4E40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36405" yWindow="2295" windowWidth="26910" windowHeight="12765" xr2:uid="{D9039836-AE1C-44B6-B79C-EC3842DC130C}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{D9039836-AE1C-44B6-B79C-EC3842DC130C}"/>
   </bookViews>
   <sheets>
     <sheet name="RDrivenShafts_HambaLG" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="39">
   <si>
     <t>Rack Displacement</t>
   </si>
@@ -147,6 +147,12 @@
   </si>
   <si>
     <t>Units</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>N/(m/s)</t>
   </si>
 </sst>
 </file>
@@ -228,7 +234,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -269,12 +275,31 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{C7FD2671-4695-42EF-B7D6-2FEFF336E27C}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -636,7 +661,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB38"/>
+  <dimension ref="A1:AB39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="2" customWidth="1"/>
@@ -773,137 +798,117 @@
         <v>19.792000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="1:28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>10</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4">
-        <v>-1.3243331220516996</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.45175517503754498</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0.88921153885340298</v>
+        <v>21</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
+      <c r="A10" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="B10" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5">
-        <v>0.35289999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>-1.3243331220516996</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.45175517503754498</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.88921153885340298</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="8"/>
       <c r="B11" s="7" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
-        <v>1</v>
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="8"/>
       <c r="B12" s="7" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C12" s="7"/>
+      <c r="D12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="12" t="s">
-        <v>16</v>
+      <c r="H12" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>15</v>
-      </c>
+      <c r="A13" s="8"/>
       <c r="B13" s="7" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="10"/>
+      <c r="H13" s="12" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
+      <c r="A14" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="B14" s="7" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="6">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
@@ -927,25 +932,43 @@
       <c r="AB14" s="10"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>14</v>
-      </c>
+      <c r="A15" s="8"/>
       <c r="B15" s="7" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="5">
-        <v>0.2</v>
-      </c>
+      <c r="H15" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
+      <c r="AA15" s="10"/>
+      <c r="AB15" s="10"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>1</v>
@@ -954,430 +977,442 @@
       <c r="D16" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
       <c r="H16" s="5">
         <v>0.2</v>
       </c>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
+      <c r="A17" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="B17" s="7" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0.4</v>
+        <v>7</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.2</v>
       </c>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>11</v>
-      </c>
+      <c r="A18" s="8"/>
       <c r="B18" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F18" s="1">
-        <v>0.13380000000000003</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0.2</v>
-      </c>
       <c r="H18" s="1">
-        <v>0.20535898384862206</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
+      <c r="A19" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="B19" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="F19" s="1">
+        <v>0.13380000000000003</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.2</v>
+      </c>
       <c r="H19" s="1">
-        <v>9.6000000000000002E-2</v>
+        <v>0.20535898384862206</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" s="7" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1">
-        <v>0.05</v>
+        <v>9.6000000000000002E-2</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>6</v>
-      </c>
+      <c r="A21" s="8"/>
       <c r="B21" s="7" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="9">
-        <f>H26*$H$27</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I21" s="9">
-        <f>I26*$H$27</f>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J21" s="9">
-        <f>J26*$H$27</f>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K21" s="9">
-        <f>K26*$H$27</f>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L21" s="9">
-        <f>L26*$H$27</f>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M21" s="9">
-        <f>M26*$H$27</f>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N21" s="9">
-        <f>N26*$H$27</f>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O21" s="9">
-        <f>O26*$H$27</f>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P21" s="9">
-        <f>P26*$H$27</f>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q21" s="9">
-        <f>Q26*$H$27</f>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R21" s="9">
-        <f>R26*$H$27</f>
-        <v>0</v>
-      </c>
-      <c r="S21" s="9">
-        <f>S26*$H$27</f>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T21" s="9">
-        <f>T26*$H$27</f>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U21" s="9">
-        <f>U26*$H$27</f>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V21" s="9">
-        <f>V26*$H$27</f>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W21" s="9">
-        <f>W26*$H$27</f>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X21" s="9">
-        <f>X26*$H$27</f>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y21" s="9">
-        <f>Y26*$H$27</f>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z21" s="9">
-        <f>Z26*$H$27</f>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA21" s="9">
-        <f>AA26*$H$27</f>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB21" s="9">
-        <f>AB26*$H$27</f>
-        <v>3.1415700000000002</v>
+        <v>7</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.05</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
+      <c r="A22" s="8" t="s">
+        <v>6</v>
+      </c>
       <c r="B22" s="7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="6">
-        <f>H24*$H$17</f>
+      <c r="H22" s="9">
+        <f t="shared" ref="H22:AB22" si="0">H27*$H$28</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I22" s="9">
+        <f t="shared" si="0"/>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA22" s="9">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB22" s="9">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="B23" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6">
+        <f t="shared" ref="H23:AB23" si="1">H25*$H$18</f>
         <v>-0.12</v>
       </c>
-      <c r="I22" s="6">
-        <f>I24*$H$17</f>
+      <c r="I23" s="6">
+        <f t="shared" si="1"/>
         <v>-0.10920000000000002</v>
       </c>
-      <c r="J22" s="6">
-        <f>J24*$H$17</f>
+      <c r="J23" s="6">
+        <f t="shared" si="1"/>
         <v>-9.7440000000000013E-2</v>
       </c>
-      <c r="K22" s="6">
-        <f>K24*$H$17</f>
+      <c r="K23" s="6">
+        <f t="shared" si="1"/>
         <v>-8.448E-2</v>
       </c>
-      <c r="L22" s="6">
-        <f>L24*$H$17</f>
+      <c r="L23" s="6">
+        <f t="shared" si="1"/>
         <v>-7.1120000000000003E-2</v>
       </c>
-      <c r="M22" s="6">
-        <f>M24*$H$17</f>
+      <c r="M23" s="6">
+        <f t="shared" si="1"/>
         <v>-5.8480000000000004E-2</v>
       </c>
-      <c r="N22" s="6">
-        <f>N24*$H$17</f>
+      <c r="N23" s="6">
+        <f t="shared" si="1"/>
         <v>-4.7120000000000002E-2</v>
       </c>
-      <c r="O22" s="6">
-        <f>O24*$H$17</f>
+      <c r="O23" s="6">
+        <f t="shared" si="1"/>
         <v>-3.6480000000000005E-2</v>
       </c>
-      <c r="P22" s="6">
-        <f>P24*$H$17</f>
+      <c r="P23" s="6">
+        <f t="shared" si="1"/>
         <v>-2.5440000000000004E-2</v>
       </c>
-      <c r="Q22" s="6">
-        <f>Q24*$H$17</f>
+      <c r="Q23" s="6">
+        <f t="shared" si="1"/>
         <v>-1.3200000000000002E-2</v>
       </c>
-      <c r="R22" s="6">
-        <f>R24*$H$17</f>
+      <c r="R23" s="6">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S22" s="6">
-        <f>S24*$H$17</f>
+      <c r="S23" s="6">
+        <f t="shared" si="1"/>
         <v>1.3200000000000002E-2</v>
       </c>
-      <c r="T22" s="6">
-        <f>T24*$H$17</f>
+      <c r="T23" s="6">
+        <f t="shared" si="1"/>
         <v>2.5440000000000004E-2</v>
       </c>
-      <c r="U22" s="6">
-        <f>U24*$H$17</f>
+      <c r="U23" s="6">
+        <f t="shared" si="1"/>
         <v>3.6480000000000005E-2</v>
       </c>
-      <c r="V22" s="6">
-        <f>V24*$H$17</f>
+      <c r="V23" s="6">
+        <f t="shared" si="1"/>
         <v>4.7120000000000002E-2</v>
       </c>
-      <c r="W22" s="6">
-        <f>W24*$H$17</f>
+      <c r="W23" s="6">
+        <f t="shared" si="1"/>
         <v>5.852000000000001E-2</v>
       </c>
-      <c r="X22" s="6">
-        <f>X24*$H$17</f>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
         <v>7.1120000000000003E-2</v>
       </c>
-      <c r="Y22" s="6">
-        <f>Y24*$H$17</f>
+      <c r="Y23" s="6">
+        <f t="shared" si="1"/>
         <v>8.448E-2</v>
       </c>
-      <c r="Z22" s="6">
-        <f>Z24*$H$17</f>
+      <c r="Z23" s="6">
+        <f t="shared" si="1"/>
         <v>9.7440000000000013E-2</v>
       </c>
-      <c r="AA22" s="6">
-        <f>AA24*$H$17</f>
+      <c r="AA23" s="6">
+        <f t="shared" si="1"/>
         <v>0.10920000000000002</v>
       </c>
-      <c r="AB22" s="6">
-        <f>AB24*$H$17</f>
+      <c r="AB23" s="6">
+        <f t="shared" si="1"/>
         <v>0.12</v>
       </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="5">
-        <v>-0.3</v>
-      </c>
-      <c r="I24" s="1">
-        <v>-0.27300000000000002</v>
-      </c>
-      <c r="J24" s="1">
-        <v>-0.24360000000000001</v>
-      </c>
-      <c r="K24" s="1">
-        <v>-0.2112</v>
-      </c>
-      <c r="L24" s="1">
-        <v>-0.17780000000000001</v>
-      </c>
-      <c r="M24" s="1">
-        <v>-0.1462</v>
-      </c>
-      <c r="N24" s="1">
-        <v>-0.1178</v>
-      </c>
-      <c r="O24" s="1">
-        <v>-9.1200000000000003E-2</v>
-      </c>
-      <c r="P24" s="1">
-        <v>-6.3600000000000004E-2</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>-3.3000000000000002E-2</v>
-      </c>
-      <c r="R24" s="1">
-        <v>0</v>
-      </c>
-      <c r="S24" s="1">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="T24" s="1">
-        <v>6.3600000000000004E-2</v>
-      </c>
-      <c r="U24" s="1">
-        <v>9.1200000000000003E-2</v>
-      </c>
-      <c r="V24" s="1">
-        <v>0.1178</v>
-      </c>
-      <c r="W24" s="1">
-        <v>0.14630000000000001</v>
-      </c>
-      <c r="X24" s="1">
-        <v>0.17780000000000001</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>0.2112</v>
-      </c>
-      <c r="Z24" s="1">
-        <v>0.24360000000000001</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="AB24" s="1">
-        <v>0.3</v>
-      </c>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="1">
+      <c r="H25" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-0.27300000000000002</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-0.24360000000000001</v>
+      </c>
+      <c r="K25" s="1">
+        <v>-0.2112</v>
+      </c>
+      <c r="L25" s="1">
+        <v>-0.17780000000000001</v>
+      </c>
+      <c r="M25" s="1">
+        <v>-0.1462</v>
+      </c>
+      <c r="N25" s="1">
+        <v>-0.1178</v>
+      </c>
+      <c r="O25" s="1">
+        <v>-9.1200000000000003E-2</v>
+      </c>
+      <c r="P25" s="1">
+        <v>-6.3600000000000004E-2</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T25" s="1">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="U25" s="1">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="V25" s="1">
+        <v>0.1178</v>
+      </c>
+      <c r="W25" s="1">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="X25" s="1">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>0.2112</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="AB25" s="1">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="1">
         <f>0.6</f>
         <v>0.6</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="H26" s="5">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="H27" s="5">
         <v>-180</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I27" s="1">
         <v>-162</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J27" s="1">
         <v>-144</v>
       </c>
-      <c r="K26" s="1">
+      <c r="K27" s="1">
         <v>-126</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L27" s="1">
         <v>-108</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M27" s="1">
         <v>-90</v>
       </c>
-      <c r="N26" s="1">
+      <c r="N27" s="1">
         <v>-72</v>
       </c>
-      <c r="O26" s="1">
+      <c r="O27" s="1">
         <v>-54</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P27" s="1">
         <v>-36</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q27" s="1">
         <v>-18</v>
       </c>
-      <c r="R26" s="1">
+      <c r="R27" s="1">
         <v>0</v>
       </c>
-      <c r="S26" s="1">
+      <c r="S27" s="1">
         <v>18</v>
       </c>
-      <c r="T26" s="1">
+      <c r="T27" s="1">
         <v>36</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U27" s="1">
         <v>54</v>
       </c>
-      <c r="V26" s="1">
+      <c r="V27" s="1">
         <v>72</v>
       </c>
-      <c r="W26" s="1">
+      <c r="W27" s="1">
         <v>90</v>
       </c>
-      <c r="X26" s="1">
+      <c r="X27" s="1">
         <v>108</v>
       </c>
-      <c r="Y26" s="1">
+      <c r="Y27" s="1">
         <v>126</v>
       </c>
-      <c r="Z26" s="1">
+      <c r="Z27" s="1">
         <v>144</v>
       </c>
-      <c r="AA26" s="1">
+      <c r="AA27" s="1">
         <v>162</v>
       </c>
-      <c r="AB26" s="1">
+      <c r="AB27" s="1">
         <v>180</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1">
-        <f>3.14157/180</f>
-        <v>1.7453166666666669E-2</v>
       </c>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="H28" s="1">
+        <f>3.14157/180</f>
+        <v>1.7453166666666669E-2</v>
+      </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F29" s="4"/>
@@ -1400,7 +1435,6 @@
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="2"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -1412,6 +1446,7 @@
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="2"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -1422,30 +1457,45 @@
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="2"/>
-      <c r="H37" s="3"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="H38" s="3"/>
     </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="2"/>
+      <c r="H39" s="3"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A37:A38">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+  <conditionalFormatting sqref="A38:A39">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B22">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="A4:B7 A9:B23">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A33:B36">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+  <conditionalFormatting sqref="A34:B37">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E22">
+  <conditionalFormatting sqref="E5 E7 E9:E23">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:B8">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
